--- a/cost_recovery_record_from_2025.xlsx
+++ b/cost_recovery_record_from_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vetdd\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsrisai\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1697AB-0CBA-46ED-B1C3-5BA3248887CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359CA43C-A2B0-4B1F-99AA-BD67D26C335B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{A65C8BF4-CB96-401D-8F12-F9A2BDA0DEB4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A65C8BF4-CB96-401D-8F12-F9A2BDA0DEB4}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>Dr. Awadh Binhazim</t>
   </si>
   <si>
-    <t>Dr. Dash Chandravanu</t>
-  </si>
-  <si>
     <t>Dr. Luciana B de Arruda</t>
   </si>
   <si>
@@ -120,6 +117,12 @@
   </si>
   <si>
     <t>Cancer_Related_Project</t>
+  </si>
+  <si>
+    <t>Dr. Chandravanu Dash</t>
+  </si>
+  <si>
+    <t>Dr. Guoliang Li</t>
   </si>
 </sst>
 </file>
@@ -166,14 +169,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,66 +510,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D03DD13-4E3A-4CD6-879D-A1B2A04A1C17}">
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.54296875" customWidth="1"/>
-    <col min="8" max="8" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" customWidth="1"/>
+    <col min="8" max="8" width="37.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="M1" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -575,12 +577,12 @@
         <v>45948</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2">
         <v>122</v>
       </c>
       <c r="F2">
@@ -588,21 +590,21 @@
       </c>
       <c r="K2" s="2"/>
       <c r="M2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2">
         <v>45915</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -614,21 +616,21 @@
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>46071</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1">
         <v>250</v>
@@ -637,21 +639,21 @@
         <v>10</v>
       </c>
       <c r="M4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2">
         <v>46076</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1">
         <v>2691</v>
@@ -663,21 +665,21 @@
         <v>276</v>
       </c>
       <c r="M5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="2">
         <v>46071</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1">
         <v>254</v>
@@ -689,50 +691,67 @@
         <v>3</v>
       </c>
       <c r="M6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2">
         <v>46072</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2">
         <v>46071</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M9" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/cost_recovery_record_from_2025.xlsx
+++ b/cost_recovery_record_from_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsrisai\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359CA43C-A2B0-4B1F-99AA-BD67D26C335B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80940D6-B25E-4862-A75D-C3D3C823E627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A65C8BF4-CB96-401D-8F12-F9A2BDA0DEB4}"/>
   </bookViews>
@@ -747,6 +747,9 @@
       <c r="C9" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
       <c r="M9" t="s">
         <v>6</v>
       </c>
